--- a/reporting_demo_portfolio.xlsx
+++ b/reporting_demo_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanyg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB36C3A3-2B82-470C-95E6-FF1931BF9B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8902633-4F16-49DE-B75A-57AE6C16332C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="18720" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard KPI" sheetId="1" r:id="rId1"/>
@@ -40,30 +40,6 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Action escalade lancée pour 3 dossiers le 07/03. Résultats attendus S12.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
     <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
@@ -78,72 +54,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Source : extraction CRM du 10/03/2026. Inclut facture contestée n°F-2024-1187 (98 400 MAD).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Taux en baisse depuis S06 — dossier en cours de renégociation. Provision recommandée.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>DSO anormalement élevé — vérifier si arriérés S47-S50 inclus dans le calcul. À reconfirmer avec extraction SI.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Baisse ponctuelle liée au congé Aïd — reprise encaissements S06.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -190,9 +100,6 @@
     <t>Segment</t>
   </si>
   <si>
-    <t>Base (MAD '000)</t>
-  </si>
-  <si>
     <t>% du total</t>
   </si>
   <si>
@@ -361,12 +268,6 @@
     <t>Période</t>
   </si>
   <si>
-    <t>Réalisé démo (MAD '000)</t>
-  </si>
-  <si>
-    <t>Cible démo (MAD '000)</t>
-  </si>
-  <si>
     <t>Écart</t>
   </si>
   <si>
@@ -413,6 +314,15 @@
   </si>
   <si>
     <t>⚠ Données fictives et reconstituées à des fins de démonstration portfolio. Aucune donnée client réelle ou d'entreprise.</t>
+  </si>
+  <si>
+    <t>Réalisé démo (MAD)</t>
+  </si>
+  <si>
+    <t>Cible démo (MAD)</t>
+  </si>
+  <si>
+    <t>Base (MAD)</t>
   </si>
 </sst>
 </file>
@@ -678,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -785,9 +695,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -816,15 +723,16 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -832,7 +740,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -985,7 +892,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Base (MAD '000)</c:v>
+                  <c:v>Base (MAD)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1120,16 +1027,16 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7320</c:v>
+                  <c:v>7320000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2540</c:v>
+                  <c:v>2540000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>930</c:v>
+                  <c:v>930000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1650</c:v>
+                  <c:v>1650000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,7 +1268,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Réalisé démo (MAD '000)</c:v>
+                  <c:v>Réalisé démo (MAD)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1463,37 +1370,37 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>2800</c:v>
+                  <c:v>2800000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3100</c:v>
+                  <c:v>3100000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2950</c:v>
+                  <c:v>2950000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3200</c:v>
+                  <c:v>3200000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2700</c:v>
+                  <c:v>2700000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3400</c:v>
+                  <c:v>3400000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3050</c:v>
+                  <c:v>3050000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2900</c:v>
+                  <c:v>2900000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3350</c:v>
+                  <c:v>3350000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3150</c:v>
+                  <c:v>3150000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3500</c:v>
+                  <c:v>3500000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1514,7 +1421,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Cible démo (MAD '000)</c:v>
+                  <c:v>Cible démo (MAD)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1616,37 +1523,37 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>3000</c:v>
+                  <c:v>3000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3000</c:v>
+                  <c:v>3000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3000</c:v>
+                  <c:v>3000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3100</c:v>
+                  <c:v>3100000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3100</c:v>
+                  <c:v>3100000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3100</c:v>
+                  <c:v>3100000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3200</c:v>
+                  <c:v>3200000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3200</c:v>
+                  <c:v>3200000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3200</c:v>
+                  <c:v>3200000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3300</c:v>
+                  <c:v>3300000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3300</c:v>
+                  <c:v>3300000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2116,7 +2023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0B1D3A"/>
   </sheetPr>
@@ -2133,49 +2040,49 @@
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2211,7 +2118,7 @@
       </c>
       <c r="H6" s="5">
         <f>Historique!C15/Segmentation!L22</f>
-        <v>2.8135048231511253E-4</v>
+        <v>0.28135048231511256</v>
       </c>
       <c r="J6" s="5">
         <f>AVERAGE(Segmentation!G12:G21)</f>
@@ -2237,42 +2144,42 @@
     </row>
     <row r="8" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="10">
-        <f>ROUND((Segmentation!C22)/1000,0)</f>
-        <v>7320</v>
+        <f>ROUND((Segmentation!C22),0)</f>
+        <v>7320000</v>
       </c>
       <c r="D11" s="11">
         <f>C11/C15</f>
@@ -2282,16 +2189,16 @@
         <v>4</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="15">
-        <f>ROUND((Segmentation!D22)/1000,0)</f>
-        <v>2540</v>
+        <f>ROUND((Segmentation!D22),0)</f>
+        <v>2540000</v>
       </c>
       <c r="D12" s="16">
         <f>C12/C15</f>
@@ -2301,16 +2208,16 @@
         <v>3</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="10">
-        <f>ROUND((Segmentation!E22)/1000,0)</f>
-        <v>930</v>
+        <f>ROUND((Segmentation!E22),0)</f>
+        <v>930000</v>
       </c>
       <c r="D13" s="11">
         <f>C13/C15</f>
@@ -2320,16 +2227,16 @@
         <v>2</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="15">
-        <f>ROUND((Segmentation!F22)/1000,0)</f>
-        <v>1650</v>
+        <f>ROUND((Segmentation!F22),0)</f>
+        <v>1650000</v>
       </c>
       <c r="D14" s="16">
         <f>C14/C15</f>
@@ -2339,77 +2246,76 @@
         <v>1</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="22">
         <f>SUM(C11:C14)</f>
-        <v>12440</v>
+        <v>12440000</v>
       </c>
       <c r="D15" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="F15" s="24"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="53" t="s">
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="53" t="s">
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+    </row>
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="58" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2433,131 +2339,131 @@
   <sheetData>
     <row r="1" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="B1" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+        <v>31</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
+        <v>32</v>
+      </c>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="53"/>
+      <c r="E6" s="25" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" s="54"/>
-      <c r="E6" s="25" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="27">
         <v>0.4</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="27">
         <v>0.3</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="27">
         <v>0.3</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="H11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="31">
         <v>1640000</v>
@@ -2585,17 +2491,17 @@
         <v>5.2085245901639343</v>
       </c>
       <c r="K12" s="35" t="str">
-        <f t="shared" ref="K12:K21" si="1">IF(J12&gt;=7,"Niveau 1",IF(J12&gt;=5,"Niveau 2",IF(J12&gt;=3,"Niveau 3","Niveau 4")))</f>
-        <v>Niveau 2</v>
+        <f>IF(J12&gt;=7,"Faible",IF(J12&gt;=5,"Moyenne",IF(J12&gt;=3,"Haute","Critique")))</f>
+        <v>Moyenne</v>
       </c>
       <c r="L12" s="36">
-        <f t="shared" ref="L12:L21" si="2">SUM(C12:F12)</f>
+        <f>SUM(C12:F12)</f>
         <v>2440000</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="37">
         <v>740000</v>
@@ -2622,18 +2528,18 @@
         <f t="shared" si="0"/>
         <v>4.1737073726659064</v>
       </c>
-      <c r="K13" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v>Niveau 3</v>
-      </c>
-      <c r="L13" s="42">
-        <f t="shared" si="2"/>
+      <c r="K13" s="35" t="str">
+        <f t="shared" ref="K13:K21" si="1">IF(J13&gt;=7,"Faible",IF(J13&gt;=5,"Moyenne",IF(J13&gt;=3,"Haute","Critique")))</f>
+        <v>Haute</v>
+      </c>
+      <c r="L13" s="36">
+        <f t="shared" ref="L13:L21" si="2">SUM(C13:F13)</f>
         <v>1870000</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="31">
         <v>1190000</v>
@@ -2662,7 +2568,7 @@
       </c>
       <c r="K14" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 2</v>
+        <v>Moyenne</v>
       </c>
       <c r="L14" s="36">
         <f t="shared" si="2"/>
@@ -2671,7 +2577,7 @@
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="37">
         <v>810000</v>
@@ -2698,18 +2604,18 @@
         <f t="shared" si="0"/>
         <v>5.6375375444227904</v>
       </c>
-      <c r="K15" s="41" t="str">
+      <c r="K15" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 2</v>
-      </c>
-      <c r="L15" s="42">
+        <v>Moyenne</v>
+      </c>
+      <c r="L15" s="36">
         <f t="shared" si="2"/>
         <v>1430000</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="31">
         <v>890000</v>
@@ -2738,7 +2644,7 @@
       </c>
       <c r="K16" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 1</v>
+        <v>Faible</v>
       </c>
       <c r="L16" s="36">
         <f t="shared" si="2"/>
@@ -2747,7 +2653,7 @@
     </row>
     <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="37">
         <v>280000</v>
@@ -2774,18 +2680,18 @@
         <f t="shared" si="0"/>
         <v>4.3479391100702571</v>
       </c>
-      <c r="K17" s="41" t="str">
+      <c r="K17" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 3</v>
-      </c>
-      <c r="L17" s="42">
+        <v>Haute</v>
+      </c>
+      <c r="L17" s="36">
         <f t="shared" si="2"/>
         <v>980000</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="31">
         <v>620000</v>
@@ -2814,7 +2720,7 @@
       </c>
       <c r="K18" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 1</v>
+        <v>Faible</v>
       </c>
       <c r="L18" s="36">
         <f t="shared" si="2"/>
@@ -2823,7 +2729,7 @@
     </row>
     <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="37">
         <v>350000</v>
@@ -2850,18 +2756,18 @@
         <f t="shared" si="0"/>
         <v>5.9245355191256834</v>
       </c>
-      <c r="K19" s="41" t="str">
+      <c r="K19" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 2</v>
-      </c>
-      <c r="L19" s="42">
+        <v>Moyenne</v>
+      </c>
+      <c r="L19" s="36">
         <f t="shared" si="2"/>
         <v>750000</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="31">
         <v>500000</v>
@@ -2890,7 +2796,7 @@
       </c>
       <c r="K20" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 1</v>
+        <v>Faible</v>
       </c>
       <c r="L20" s="36">
         <f t="shared" si="2"/>
@@ -2899,7 +2805,7 @@
     </row>
     <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="37">
         <v>300000</v>
@@ -2926,90 +2832,90 @@
         <f t="shared" si="0"/>
         <v>6.2872131147540991</v>
       </c>
-      <c r="K21" s="41" t="str">
+      <c r="K21" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>Niveau 2</v>
-      </c>
-      <c r="L21" s="42">
+        <v>Moyenne</v>
+      </c>
+      <c r="L21" s="36">
         <f t="shared" si="2"/>
         <v>610000</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="44">
+      <c r="B22" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="43">
         <f>SUM(C12:C21)</f>
         <v>7320000</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="43">
         <f>SUM(D12:D21)</f>
         <v>2540000</v>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="43">
         <f>SUM(E12:E21)</f>
         <v>930000</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="43">
         <f>SUM(F12:F21)</f>
         <v>1650000</v>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="44">
         <f>AVERAGE(G12:G21)</f>
         <v>0.76899999999999991</v>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="45">
         <f>AVERAGE(H12:H21)</f>
         <v>53.8</v>
       </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="48">
+      <c r="I22" s="46"/>
+      <c r="J22" s="47">
         <f>AVERAGE(J12:J21)</f>
         <v>6.1025726763854946</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="44">
+      <c r="K22" s="46"/>
+      <c r="L22" s="43">
         <f>SUM(L12:L21)</f>
         <v>12440000</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="63"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
     </row>
     <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+    </row>
+    <row r="26" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B26" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="54"/>
-    </row>
-    <row r="26" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B26" s="52" t="s">
+    </row>
+    <row r="27" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B27" s="51" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B27" s="52" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3028,7 +2934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFB8520E"/>
   </sheetPr>
@@ -3048,384 +2954,384 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="4" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" s="31">
-        <v>2800</v>
+        <v>2800000</v>
       </c>
       <c r="D5" s="31">
-        <v>3000</v>
+        <v>3000000</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ref="E5:E16" si="0">C5-D5</f>
-        <v>-200</v>
-      </c>
-      <c r="F5" s="49">
+        <v>-200000</v>
+      </c>
+      <c r="F5" s="48">
         <f t="shared" ref="F5:F16" si="1">C5/D5</f>
         <v>0.93333333333333335</v>
       </c>
       <c r="G5" s="10">
         <f>C5</f>
-        <v>2800</v>
-      </c>
-      <c r="H5" s="49">
+        <v>2800000</v>
+      </c>
+      <c r="H5" s="48">
         <f>C5/Segmentation!L22</f>
-        <v>2.2508038585209003E-4</v>
+        <v>0.22508038585209003</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" s="37">
-        <v>3100</v>
+        <v>3100000</v>
       </c>
       <c r="D6" s="37">
-        <v>3000</v>
+        <v>3000000</v>
       </c>
       <c r="E6" s="15">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F6" s="50">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="49">
         <f t="shared" si="1"/>
         <v>1.0333333333333334</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" ref="G6:G15" si="2">G5+C6</f>
-        <v>5900</v>
-      </c>
-      <c r="H6" s="50">
+        <v>5900000</v>
+      </c>
+      <c r="H6" s="49">
         <f>C6/Segmentation!L22</f>
-        <v>2.4919614147909968E-4</v>
+        <v>0.24919614147909969</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C7" s="31">
-        <v>2950</v>
+        <v>2950000</v>
       </c>
       <c r="D7" s="31">
-        <v>3000</v>
+        <v>3000000</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="F7" s="49">
+        <v>-50000</v>
+      </c>
+      <c r="F7" s="48">
         <f t="shared" si="1"/>
         <v>0.98333333333333328</v>
       </c>
       <c r="G7" s="10">
         <f t="shared" si="2"/>
-        <v>8850</v>
-      </c>
-      <c r="H7" s="49">
+        <v>8850000</v>
+      </c>
+      <c r="H7" s="48">
         <f>C7/Segmentation!L22</f>
-        <v>2.3713826366559486E-4</v>
+        <v>0.23713826366559485</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="41" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" s="37">
-        <v>3200</v>
+        <v>3200000</v>
       </c>
       <c r="D8" s="37">
-        <v>3100</v>
+        <v>3100000</v>
       </c>
       <c r="E8" s="15">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="F8" s="50">
+        <v>100000</v>
+      </c>
+      <c r="F8" s="49">
         <f t="shared" si="1"/>
         <v>1.032258064516129</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="2"/>
-        <v>12050</v>
-      </c>
-      <c r="H8" s="50">
+        <v>12050000</v>
+      </c>
+      <c r="H8" s="49">
         <f>C8/Segmentation!L22</f>
-        <v>2.5723472668810288E-4</v>
+        <v>0.25723472668810288</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" s="31">
-        <v>2700</v>
+        <v>2700000</v>
       </c>
       <c r="D9" s="31">
-        <v>3100</v>
+        <v>3100000</v>
       </c>
       <c r="E9" s="10">
         <f t="shared" si="0"/>
-        <v>-400</v>
-      </c>
-      <c r="F9" s="49">
+        <v>-400000</v>
+      </c>
+      <c r="F9" s="48">
         <f t="shared" si="1"/>
         <v>0.87096774193548387</v>
       </c>
       <c r="G9" s="10">
         <f t="shared" si="2"/>
-        <v>14750</v>
-      </c>
-      <c r="H9" s="49">
+        <v>14750000</v>
+      </c>
+      <c r="H9" s="48">
         <f>C9/Segmentation!L22</f>
-        <v>2.1704180064308681E-4</v>
+        <v>0.21704180064308681</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C10" s="37">
-        <v>3400</v>
+        <v>3400000</v>
       </c>
       <c r="D10" s="37">
-        <v>3100</v>
+        <v>3100000</v>
       </c>
       <c r="E10" s="15">
         <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="F10" s="50">
+        <v>300000</v>
+      </c>
+      <c r="F10" s="49">
         <f t="shared" si="1"/>
         <v>1.096774193548387</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="2"/>
-        <v>18150</v>
-      </c>
-      <c r="H10" s="50">
+        <v>18150000</v>
+      </c>
+      <c r="H10" s="49">
         <f>C10/Segmentation!L22</f>
-        <v>2.7331189710610933E-4</v>
+        <v>0.27331189710610931</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="35" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" s="31">
-        <v>3050</v>
+        <v>3050000</v>
       </c>
       <c r="D11" s="31">
-        <v>3200</v>
+        <v>3200000</v>
       </c>
       <c r="E11" s="10">
         <f t="shared" si="0"/>
-        <v>-150</v>
-      </c>
-      <c r="F11" s="49">
+        <v>-150000</v>
+      </c>
+      <c r="F11" s="48">
         <f t="shared" si="1"/>
         <v>0.953125</v>
       </c>
       <c r="G11" s="10">
         <f t="shared" si="2"/>
-        <v>21200</v>
-      </c>
-      <c r="H11" s="49">
+        <v>21200000</v>
+      </c>
+      <c r="H11" s="48">
         <f>C11/Segmentation!L22</f>
-        <v>2.4517684887459805E-4</v>
+        <v>0.24517684887459806</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="37">
-        <v>2900</v>
+        <v>2900000</v>
       </c>
       <c r="D12" s="37">
-        <v>3200</v>
+        <v>3200000</v>
       </c>
       <c r="E12" s="15">
         <f t="shared" si="0"/>
-        <v>-300</v>
-      </c>
-      <c r="F12" s="50">
+        <v>-300000</v>
+      </c>
+      <c r="F12" s="49">
         <f t="shared" si="1"/>
         <v>0.90625</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="2"/>
-        <v>24100</v>
-      </c>
-      <c r="H12" s="50">
+        <v>24100000</v>
+      </c>
+      <c r="H12" s="49">
         <f>C12/Segmentation!L22</f>
-        <v>2.3311897106109326E-4</v>
+        <v>0.23311897106109325</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" s="31">
-        <v>3350</v>
+        <v>3350000</v>
       </c>
       <c r="D13" s="31">
-        <v>3200</v>
+        <v>3200000</v>
       </c>
       <c r="E13" s="10">
         <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="F13" s="49">
+        <v>150000</v>
+      </c>
+      <c r="F13" s="48">
         <f t="shared" si="1"/>
         <v>1.046875</v>
       </c>
       <c r="G13" s="10">
         <f t="shared" si="2"/>
-        <v>27450</v>
-      </c>
-      <c r="H13" s="49">
+        <v>27450000</v>
+      </c>
+      <c r="H13" s="48">
         <f>C13/Segmentation!L22</f>
-        <v>2.692926045016077E-4</v>
+        <v>0.26929260450160769</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C14" s="37">
-        <v>3150</v>
+        <v>3150000</v>
       </c>
       <c r="D14" s="37">
-        <v>3300</v>
+        <v>3300000</v>
       </c>
       <c r="E14" s="15">
         <f t="shared" si="0"/>
-        <v>-150</v>
-      </c>
-      <c r="F14" s="50">
+        <v>-150000</v>
+      </c>
+      <c r="F14" s="49">
         <f t="shared" si="1"/>
         <v>0.95454545454545459</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="2"/>
-        <v>30600</v>
-      </c>
-      <c r="H14" s="50">
+        <v>30600000</v>
+      </c>
+      <c r="H14" s="49">
         <f>C14/Segmentation!L22</f>
-        <v>2.5321543408360131E-4</v>
+        <v>0.25321543408360131</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C15" s="31">
-        <v>3500</v>
+        <v>3500000</v>
       </c>
       <c r="D15" s="31">
-        <v>3300</v>
+        <v>3300000</v>
       </c>
       <c r="E15" s="10">
         <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-      <c r="F15" s="49">
+        <v>200000</v>
+      </c>
+      <c r="F15" s="48">
         <f t="shared" si="1"/>
         <v>1.0606060606060606</v>
       </c>
       <c r="G15" s="10">
         <f t="shared" si="2"/>
-        <v>34100</v>
-      </c>
-      <c r="H15" s="49">
+        <v>34100000</v>
+      </c>
+      <c r="H15" s="48">
         <f>C15/Segmentation!L22</f>
-        <v>2.8135048231511253E-4</v>
+        <v>0.28135048231511256</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="22">
         <f>SUM(C5:C15)</f>
-        <v>34100</v>
+        <v>34100000</v>
       </c>
       <c r="D16" s="22">
         <f>SUM(D5:D15)</f>
-        <v>34500</v>
+        <v>34500000</v>
       </c>
       <c r="E16" s="22">
         <f t="shared" si="0"/>
-        <v>-400</v>
-      </c>
-      <c r="F16" s="45">
+        <v>-400000</v>
+      </c>
+      <c r="F16" s="44">
         <f t="shared" si="1"/>
         <v>0.98840579710144927</v>
       </c>
       <c r="G16" s="22">
         <f>SUM(G15)</f>
-        <v>34100</v>
-      </c>
-      <c r="H16" s="51"/>
+        <v>34100000</v>
+      </c>
+      <c r="H16" s="50"/>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
+      <c r="B34" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3436,6 +3342,5 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>